--- a/files/九龙-何文田-朗贤峰第IIA期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIA期.xlsx
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -11654,14 +11654,14 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
         <v>25297000</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>26133</v>
+        <v>26106</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>25297000</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>26133</v>
+        <v>26106</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -20652,7 +20652,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -21296,7 +21296,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -21420,7 +21420,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -21754,7 +21754,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -21816,7 +21816,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -22088,7 +22088,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -22150,7 +22150,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -23252,7 +23252,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -23624,7 +23624,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -23748,7 +23748,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -23810,7 +23810,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -23872,7 +23872,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -23996,7 +23996,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -24058,7 +24058,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -24182,7 +24182,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -24244,7 +24244,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -24430,7 +24430,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -24492,7 +24492,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -24740,7 +24740,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -24988,7 +24988,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -25050,7 +25050,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -25112,7 +25112,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -25174,7 +25174,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -25298,7 +25298,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -25360,7 +25360,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -25422,7 +25422,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -25484,7 +25484,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -25546,7 +25546,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -25608,7 +25608,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -25794,7 +25794,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -25918,7 +25918,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -25980,7 +25980,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -26104,7 +26104,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -26228,7 +26228,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -26414,7 +26414,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -26476,7 +26476,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -26724,7 +26724,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -26910,7 +26910,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -27220,7 +27220,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -27282,7 +27282,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -27344,7 +27344,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -27716,7 +27716,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -27778,7 +27778,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -28252,7 +28252,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -28675,7 +28675,7 @@
           <t>C | 1271呎 (4+房)
 $3503万
 $27,563/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -28683,7 +28683,7 @@
           <t>D | 1333呎 (4+房)
 $3681万
 $27,617/呎
-(24年-06月-11日)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -28709,7 +28709,7 @@
           <t>B | 1433呎 (4+房)
 $4133万
 $28,841/呎
-(24年-10月-02日)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -28725,7 +28725,7 @@
           <t>D | 1333呎 (4+房)
 $3645万
 $27,344/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -28835,7 +28835,7 @@
           <t>B | 1433呎 (4+房)
 $3992万
 $27,856/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -28843,7 +28843,7 @@
           <t>C | 1271呎 (4+房)
 $3377万
 $26,569/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -28851,7 +28851,7 @@
           <t>D | 1333呎 (4+房)
 $3468万
 $26,015/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
           <t>B | 1433呎 (4+房)
 $3932万
 $27,441/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -28893,7 +28893,7 @@
           <t>D | 1333呎 (4+房)
 $3503万
 $26,281/呎
-(24年-06月-10日)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -28911,7 +28911,7 @@
           <t>A | 998呎 (3房)
 $2477万
 $24,822/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -28919,7 +28919,7 @@
           <t>B | 797呎 (3房)
 $1991万
 $24,979/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -28935,7 +28935,7 @@
           <t>D | 685呎 (3房)
 $1515万
 $22,118/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -28943,7 +28943,7 @@
           <t>E | 482呎 (2房)
 $1073万
 $22,266/呎
-(24年-10月-11日)</t>
+(24年-10月-12日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -28951,7 +28951,7 @@
           <t>F | 482呎 (2房)
 $1061万
 $22,012/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -28959,7 +28959,7 @@
           <t>G | 624呎 (2房)
 $1339万
 $21,452/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
           <t>A | 998呎 (3房)
 $2528万
 $25,329/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>B | 797呎 (3房)
 $1986万
 $24,917/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -28990,7 +28990,7 @@
           <t>C | 998呎 (3房)
 $2477万
 $24,818/呎
-(24年-06月-16日)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -28998,7 +28998,7 @@
           <t>D | 636呎 (2房)
 $1404万
 $22,072/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -29006,7 +29006,7 @@
           <t>E | 482呎 (2房)
 $1071万
 $22,212/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -29014,7 +29014,7 @@
           <t>F | 482呎 (2房)
 $1052万
 $21,824/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -29037,7 +29037,7 @@
           <t>A | 998呎 (3房)
 $2478万
 $24,835/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>C | 998呎 (3房)
 $2514万
 $25,188/呎
-(24年-07月-04日)</t>
+(24年-07月-05日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -29061,7 +29061,7 @@
           <t>D | 636呎 (2房)
 $1397万
 $21,964/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>E | 482呎 (2房)
 $1065万
 $22,102/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -29077,7 +29077,7 @@
           <t>F | 482呎 (2房)
 $1047万
 $21,716/呎
-(24年-09月-26日)</t>
+(24年-09月-27日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -29100,7 +29100,7 @@
           <t>A | 998呎 (3房)
 $2446万
 $24,512/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -29108,7 +29108,7 @@
           <t>B | 797呎 (3房)
 $1966万
 $24,670/呎
-(24年-12月-22日)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -29124,7 +29124,7 @@
           <t>D | 636呎 (2房)
 $1390万
 $21,855/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -29132,7 +29132,7 @@
           <t>E | 482呎 (2房)
 $1060万
 $21,992/呎
-(24年-10月-02日)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -29140,7 +29140,7 @@
           <t>F | 482呎 (2房)
 $1042万
 $21,610/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -29163,7 +29163,7 @@
           <t>A | 998呎 (3房)
 $2435万
 $24,397/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -29171,7 +29171,7 @@
           <t>B | 797呎 (3房)
 $1996万
 $25,048/呎
-(24年-06月-17日)</t>
+(24年-06月-18日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -29187,7 +29187,7 @@
           <t>D | 636呎 (2房)
 $1383万
 $21,747/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -29195,7 +29195,7 @@
           <t>E | 482呎 (2房)
 $1055万
 $21,884/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -29203,7 +29203,7 @@
           <t>F | 482呎 (2房)
 $1036万
 $21,502/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -29226,7 +29226,7 @@
           <t>A | 998呎 (3房)
 $2484万
 $24,888/呎
-(24年-06月-17日)</t>
+(24年-06月-18日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -29234,7 +29234,7 @@
           <t>B | 797呎 (3房)
 $1956万
 $24,547/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29266,7 +29266,7 @@
           <t>F | 482呎 (2房)
 $1036万
 $21,502/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -29289,7 +29289,7 @@
           <t>A | 998呎 (3房)
 $2410万
 $24,149/呎
-(24年-12月-22日)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -29329,7 +29329,7 @@
           <t>F | 482呎 (2房)
 $1026万
 $21,290/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -29352,7 +29352,7 @@
           <t>A | 998呎 (3房)
 $2398万
 $24,030/呎
-(24年-06月-26日)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -29415,7 +29415,7 @@
           <t>A | 998呎 (3房)
 $2386万
 $23,910/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -29604,7 +29604,7 @@
           <t>A | 948呎 (3房)
 $2666万
 $28,122/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -29959,7 +29959,7 @@
           <t>E | 968呎 (3房)
 $2551万
 $26,352/呎
-(24年-07月-21日)</t>
+(24年-07月-22日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr"/>
@@ -30074,7 +30074,7 @@
           <t>A | 1432呎 (4+房)
 $4048万
 $28,267/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -30090,7 +30090,7 @@
           <t>C | 926呎 (3房)
 $2402万
 $25,943/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -30106,7 +30106,7 @@
           <t>E | 968呎 (3房)
 $2530万
 $26,136/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr"/>
@@ -30123,7 +30123,7 @@
           <t>A | 1432呎 (4+房)
 $4005万
 $27,968/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -30155,7 +30155,7 @@
           <t>E | 968呎 (3房)
 $2452万
 $25,331/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr"/>
@@ -30201,10 +30201,10 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>E | 968呎 (3房)
+          <t>E | 969呎 (3房)
 $2530万
-$26,133/呎
-(24年-05月-22日)</t>
+$26,106/呎
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr"/>
@@ -30253,7 +30253,7 @@
           <t>E | 968呎 (3房)
 $2427万
 $25,072/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr"/>
@@ -30270,7 +30270,7 @@
           <t>A | 1432呎 (4+房)
 $3828万
 $26,732/呎
-(24年-10月-07日)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -30302,7 +30302,7 @@
           <t>E | 968呎 (3房)
 $2428万
 $25,087/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr"/>
@@ -30335,7 +30335,7 @@
           <t>C | 926呎 (3房)
 $2268万
 $24,492/呎
-(24年-10月-20日)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -30351,7 +30351,7 @@
           <t>E | 968呎 (3房)
 $2338万
 $24,153/呎
-(24年-10月-01日)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr"/>
@@ -31061,7 +31061,7 @@
           <t>A | 946呎 (3房)
 $2779万
 $29,378/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -31069,7 +31069,7 @@
           <t>B | 753呎 (3房)
 $2305万
 $30,608/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -31077,7 +31077,7 @@
           <t>C | 942呎 (3房)
 $2829万
 $30,035/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -31335,7 +31335,7 @@
           <t>A | 988呎 (3房)
 $2392万
 $24,209/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -31351,7 +31351,7 @@
           <t>C | 899呎 (3房)
 $2217万
 $24,665/呎
-(24年-07月-15日)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -31391,7 +31391,7 @@
           <t>A | 988呎 (3房)
 $2262万
 $22,898/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -31407,7 +31407,7 @@
           <t>C | 899呎 (3房)
 $2150万
 $23,910/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -31447,7 +31447,7 @@
           <t>A | 992呎 (3房)
 $2262万
 $22,799/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -31463,7 +31463,7 @@
           <t>C | 899呎 (3房)
 $2140万
 $23,808/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -31471,7 +31471,7 @@
           <t>D | 970呎 (3房)
 $2542万
 $26,206/呎
-(24年-06月-06日)</t>
+(24年-06月-07日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -31503,7 +31503,7 @@
           <t>A | 991呎 (3房)
 $2250万
 $22,705/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -31511,7 +31511,7 @@
           <t>B | 725呎 (3房)
 $1758万
 $24,254/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -31519,7 +31519,7 @@
           <t>C | 899呎 (3房)
 $2128万
 $23,673/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -31527,7 +31527,7 @@
           <t>D | 970呎 (3房)
 $2520万
 $25,979/呎
-(24年-06月-10日)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -31559,7 +31559,7 @@
           <t>A | 992呎 (3房)
 $2283万
 $23,018/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -31567,7 +31567,7 @@
           <t>B | 725呎 (3房)
 $1760万
 $24,280/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -31575,7 +31575,7 @@
           <t>C | 899呎 (3房)
 $2161万
 $24,036/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -31583,7 +31583,7 @@
           <t>D | 970呎 (3房)
 $2492万
 $25,692/呎
-(24年-06月-06日)</t>
+(24年-06月-07日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -31599,7 +31599,7 @@
           <t>F | 924呎 (3房)
 $2341万
 $25,333/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr"/>
@@ -31615,7 +31615,7 @@
           <t>A | 992呎 (3房)
 $2227万
 $22,446/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -31623,7 +31623,7 @@
           <t>B | 725呎 (3房)
 $1783万
 $24,597/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -31631,7 +31631,7 @@
           <t>C | 899呎 (3房)
 $2119万
 $23,566/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -31639,7 +31639,7 @@
           <t>D | 970呎 (3房)
 $2468万
 $25,438/呎
-(24年-06月-12日)</t>
+(24年-06月-13日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -31671,7 +31671,7 @@
           <t>A | 992呎 (3房)
 $2216万
 $22,335/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -31679,7 +31679,7 @@
           <t>B | 725呎 (3房)
 $1732万
 $23,895/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -31687,7 +31687,7 @@
           <t>C | 899呎 (3房)
 $2097万
 $23,323/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -31727,7 +31727,7 @@
           <t>A | 992呎 (3房)
 $2226万
 $22,435/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -31735,7 +31735,7 @@
           <t>B | 725呎 (3房)
 $1732万
 $23,895/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -31743,7 +31743,7 @@
           <t>C | 899呎 (3房)
 $2107万
 $23,439/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -31783,7 +31783,7 @@
           <t>A | 992呎 (3房)
 $2238万
 $22,566/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -31791,7 +31791,7 @@
           <t>B | 725呎 (3房)
 $1715万
 $23,658/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -31799,7 +31799,7 @@
           <t>C | 899呎 (3房)
 $2118万
 $23,564/呎
-(24年-06月-05日)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -31839,7 +31839,7 @@
           <t>A | 992呎 (3房)
 $2237万
 $22,553/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -31847,7 +31847,7 @@
           <t>B | 725呎 (3房)
 $1707万
 $23,541/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -31855,7 +31855,7 @@
           <t>C | 899呎 (3房)
 $2063万
 $22,948/呎
-(24年-06月-11日)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -31895,7 +31895,7 @@
           <t>A | 992呎 (3房)
 $2216万
 $22,342/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -31903,7 +31903,7 @@
           <t>B | 725呎 (3房)
 $1709万
 $23,567/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -31911,7 +31911,7 @@
           <t>C | 899呎 (3房)
 $2098万
 $23,336/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -31919,7 +31919,7 @@
           <t>D | 682呎 (2房)
 $1413万
 $20,713/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -31927,7 +31927,7 @@
           <t>E | 490呎 (2房)
 $1022万
 $20,859/呎
-(24年-09月-26日)</t>
+(24年-09月-27日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -31935,7 +31935,7 @@
           <t>F | 490呎 (2房)
 $1032万
 $21,061/呎
-(24年-09月-26日)</t>
+(24年-09月-27日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -31943,7 +31943,7 @@
           <t>G | 601呎 (2房)
 $1231万
 $20,488/呎
-(24年-09月-29日)</t>
+(24年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -31958,7 +31958,7 @@
           <t>A | 992呎 (3房)
 $2162万
 $21,794/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -31966,7 +31966,7 @@
           <t>B | 725呎 (3房)
 $1690万
 $23,308/呎
-(24年-11月-13日)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -31974,7 +31974,7 @@
           <t>C | 899呎 (3房)
 $2045万
 $22,750/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -31982,7 +31982,7 @@
           <t>D | 629呎 (2房)
 $1300万
 $20,671/呎
-(24年-09月-22日)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -31990,7 +31990,7 @@
           <t>E | 490呎 (2房)
 $1020万
 $20,808/呎
-(24年-10月-02日)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -31998,7 +31998,7 @@
           <t>F | 490呎 (2房)
 $1029万
 $21,008/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -32006,7 +32006,7 @@
           <t>G | 601呎 (2房)
 $1228万
 $20,438/呎
-(24年-09月-23日)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
     </row>
@@ -32021,7 +32021,7 @@
           <t>A | 991呎 (3房)
 $2194万
 $22,143/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -32029,7 +32029,7 @@
           <t>B | 725呎 (3房)
 $1682万
 $23,193/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -32037,7 +32037,7 @@
           <t>C | 899呎 (3房)
 $2035万
 $22,637/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -32045,7 +32045,7 @@
           <t>D | 629呎 (2房)
 $1286万
 $20,444/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -32053,7 +32053,7 @@
           <t>E | 490呎 (2房)
 $1008万
 $20,580/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -32061,7 +32061,7 @@
           <t>F | 490呎 (2房)
 $1024万
 $20,904/呎
-(24年-09月-29日)</t>
+(24年-09月-30日)</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -32069,7 +32069,7 @@
           <t>G | 601呎 (2房)
 $1230万
 $20,461/呎
-(24年-10月-02日)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -32084,7 +32084,7 @@
           <t>A | 992呎 (3房)
 $2183万
 $22,010/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -32092,7 +32092,7 @@
           <t>B | 725呎 (3房)
 $1673万
 $23,077/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -32100,7 +32100,7 @@
           <t>C | 899呎 (3房)
 $2025万
 $22,525/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -32108,7 +32108,7 @@
           <t>D | 629呎 (2房)
 $1280万
 $20,342/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -32116,7 +32116,7 @@
           <t>E | 490呎 (2房)
 $1010万
 $20,604/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -32124,7 +32124,7 @@
           <t>F | 490呎 (2房)
 $1019万
 $20,802/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -32132,7 +32132,7 @@
           <t>G | 601呎 (2房)
 $1216万
 $20,235/呎
-(24年-10月-09日)</t>
+(24年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -32147,7 +32147,7 @@
           <t>A | 992呎 (3房)
 $2129万
 $21,463/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -32155,7 +32155,7 @@
           <t>B | 725呎 (3房)
 $1675万
 $23,101/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -32163,7 +32163,7 @@
           <t>C | 899呎 (3房)
 $2017万
 $22,435/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -32171,7 +32171,7 @@
           <t>D | 629呎 (2房)
 $1281万
 $20,366/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -32179,7 +32179,7 @@
           <t>E | 490呎 (2房)
 $998万
 $20,378/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -32187,7 +32187,7 @@
           <t>F | 490呎 (2房)
 $1008万
 $20,573/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -32195,7 +32195,7 @@
           <t>G | 601呎 (2房)
 $1218万
 $20,258/呎
-(24年-10月-20日)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -32210,7 +32210,7 @@
           <t>A | 992呎 (3房)
 $2173万
 $21,901/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -32218,7 +32218,7 @@
           <t>B | 725呎 (3房)
 $1675万
 $23,101/呎
-(24年-10月-01日)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -32226,7 +32226,7 @@
           <t>C | 899呎 (3房)
 $2015万
 $22,413/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -32234,7 +32234,7 @@
           <t>D | 629呎 (2房)
 $1273万
 $20,242/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -32242,7 +32242,7 @@
           <t>E | 490呎 (2房)
 $998万
 $20,378/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -32250,7 +32250,7 @@
           <t>F | 490呎 (2房)
 $1008万
 $20,573/呎
-(24年-10月-08日)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -32258,7 +32258,7 @@
           <t>G | 601呎 (2房)
 $1218万
 $20,258/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
           <t>A | 992呎 (3房)
 $2110万
 $21,266/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -32281,7 +32281,7 @@
           <t>B | 725呎 (3房)
 $1648万
 $22,735/呎
-(24年-10月-01日)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -32289,7 +32289,7 @@
           <t>C | 899呎 (3房)
 $2036万
 $22,646/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -32297,7 +32297,7 @@
           <t>D | 629呎 (2房)
 $1261万
 $20,043/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -32305,7 +32305,7 @@
           <t>E | 490呎 (2房)
 $995万
 $20,300/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
@@ -32313,7 +32313,7 @@
           <t>F | 490呎 (2房)
 $998万
 $20,371/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -32321,7 +32321,7 @@
           <t>G | 601呎 (2房)
 $1198万
 $19,937/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -32336,7 +32336,7 @@
           <t>A | 992呎 (3房)
 $2101万
 $21,180/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -32344,7 +32344,7 @@
           <t>B | 725呎 (3房)
 $1640万
 $22,623/呎
-(24年-09月-22日)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -32352,7 +32352,7 @@
           <t>C | 899呎 (3房)
 $2026万
 $22,532/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -32360,7 +32360,7 @@
           <t>D | 629呎 (2房)
 $1242万
 $19,749/呎
-(24年-11月-13日)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -32368,7 +32368,7 @@
           <t>E | 490呎 (2房)
 $980万
 $20,002/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -32376,7 +32376,7 @@
           <t>F | 490呎 (2房)
 $984万
 $20,071/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -32384,7 +32384,7 @@
           <t>G | 601呎 (2房)
 $1181万
 $19,644/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -32399,7 +32399,7 @@
           <t>A | 992呎 (3房)
 $2130万
 $21,470/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -32407,7 +32407,7 @@
           <t>B | 725呎 (3房)
 $1642万
 $22,647/呎
-(24年-10月-01日)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -32415,7 +32415,7 @@
           <t>C | 899呎 (3房)
 $1980万
 $22,024/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -32423,7 +32423,7 @@
           <t>D | 629呎 (2房)
 $1224万
 $19,458/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -32431,7 +32431,7 @@
           <t>E | 490呎 (2房)
 $960万
 $19,590/呎
-(24年-12月-26日)</t>
+(24年-12月-27日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -32439,7 +32439,7 @@
           <t>F | 490呎 (2房)
 $975万
 $19,898/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -32447,7 +32447,7 @@
           <t>G | 601呎 (2房)
 $1170万
 $19,474/呎
-(24年-10月-02日)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -32462,7 +32462,7 @@
           <t>A | 992呎 (3房)
 $2121万
 $21,381/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -32470,7 +32470,7 @@
           <t>B | 725呎 (3房)
 $1624万
 $22,399/呎
-(24年-10月-06日)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -32478,7 +32478,7 @@
           <t>C | 899呎 (3房)
 $2006万
 $22,309/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -32525,7 +32525,7 @@
           <t>A | 992呎 (3房)
 $2088万
 $21,048/呎
-(24年-06月-11日)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -32533,7 +32533,7 @@
           <t>B | 725呎 (3房)
 $1616万
 $22,288/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -32541,7 +32541,7 @@
           <t>C | 899呎 (3房)
 $1996万
 $22,198/呎
-(24年-06月-17日)</t>
+(24年-06月-18日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -32588,7 +32588,7 @@
           <t>A | 948呎 (3房)
 $2558万
 $26,982/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -32604,7 +32604,7 @@
           <t>C | 846呎 (3房)
 $2359万
 $27,882/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
